--- a/artfynd/A 22601-2025 artfynd.xlsx
+++ b/artfynd/A 22601-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>83557353</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>642621.0697914968</v>
+        <v>642621</v>
       </c>
       <c r="R2" t="n">
-        <v>6698524.81698467</v>
+        <v>6698525</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,19 +752,9 @@
           <t>2013-09-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-09-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Sundström, Eva Jonasson, Toy Ståhl</t>
+          <t>Andreas Sundström, Toy Ståhl, Eva Jonasson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -803,12 +788,7 @@
         <v>83557360</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>642605.838331402</v>
+        <v>642606</v>
       </c>
       <c r="R3" t="n">
-        <v>6698534.112734968</v>
+        <v>6698534</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -882,19 +862,9 @@
           <t>2013-09-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-09-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +884,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Sundström, Eva Jonasson, Toy Ståhl</t>
+          <t>Andreas Sundström, Toy Ståhl, Eva Jonasson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 22601-2025 artfynd.xlsx
+++ b/artfynd/A 22601-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83557353</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,8 +902,17 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83557360</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>